--- a/xlsx/tests/templates/crossword.xlsx
+++ b/xlsx/tests/templates/crossword.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dg-ac/Documents/IronCalc Mkt/Templates/final/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dg-ac/Documents/IronCalc Mkt/Templates/v0.9/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744B4130-4EE6-EA49-BB57-2DC3BCC1B1AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB852F78-89C2-8F4A-B662-7B24E5F9C4A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-18780" windowWidth="34220" windowHeight="17260" xr2:uid="{2706468E-7EAE-D749-B249-51B331F89E88}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{2706468E-7EAE-D749-B249-51B331F89E88}"/>
   </bookViews>
   <sheets>
     <sheet name="Crossword" sheetId="1" r:id="rId1"/>
@@ -62,20 +62,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="38">
   <si>
     <t>HOW THIS CROSSWORD WORKS</t>
   </si>
   <si>
-    <t>• Type ONE letter per white square in the grid below. Clues are on the right side.</t>
-  </si>
-  <si>
-    <t>• Correct letters turn GREEN automatically; wrong letters turn RED.</t>
-  </si>
-  <si>
-    <t>• Track your progress on the right. The answer key lives on the hidden 'Key' sheet.</t>
-  </si>
-  <si>
     <t>CROSSWORD ▣ Spreadsheet Edition</t>
   </si>
   <si>
@@ -182,13 +173,18 @@
   </si>
   <si>
     <t>Complete:</t>
+  </si>
+  <si>
+    <t>• Type ONE letter per white square in the grid below. Clues are on the right side.
+• Correct letters turn GREEN automatically; wrong letters turn RED.
+• Track your progress on the right. The answer key lives on the hidden 'Key' sheet.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -200,13 +196,6 @@
       <b/>
       <sz val="16"/>
       <color rgb="FF92D050"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
@@ -231,16 +220,51 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -263,28 +287,45 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="1" tint="0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -657,232 +698,272 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{7435519D-7569-624E-A753-681F12F308C2}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;59c5b261-57e0-4864-95aa-ecc1fb9f8a1b&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3013A7C1-D964-3D43-A9E4-35B9778E8A68}">
-  <dimension ref="B1:M25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="B1:O23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="11" width="3.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
+    <row r="1" spans="2:15" ht="20" customHeight="1"/>
+    <row r="2" spans="2:15" ht="20" customHeight="1">
+      <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
+    <row r="3" spans="2:15" ht="55" customHeight="1">
+      <c r="B3" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+    </row>
+    <row r="4" spans="2:15" ht="20" customHeight="1"/>
+    <row r="5" spans="2:15" ht="20" customHeight="1">
+      <c r="B5" s="12" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L7" s="4" t="s">
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="L5" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" ht="20" customHeight="1">
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="L6" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" ht="20" customHeight="1">
+      <c r="B7" s="11"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="L7" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" ht="20" customHeight="1">
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="L8" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="L8" s="6" t="s">
+    <row r="9" spans="2:15" ht="20" customHeight="1">
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="L9" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="L9" t="s">
+    <row r="10" spans="2:15" ht="20" customHeight="1">
+      <c r="B10" s="10"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="10"/>
+      <c r="L10" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="L10" t="s">
+    <row r="11" spans="2:15" ht="20" customHeight="1">
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="10"/>
+      <c r="L11" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="L11" t="s">
+    <row r="12" spans="2:15" ht="20" customHeight="1">
+      <c r="B12" s="10"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="10"/>
+    </row>
+    <row r="13" spans="2:15" ht="20" customHeight="1">
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="10"/>
+      <c r="L13" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="L12" t="s">
+    <row r="14" spans="2:15" ht="20" customHeight="1">
+      <c r="B14" s="10"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="L14" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="L13" t="s">
+    <row r="15" spans="2:15" ht="20" customHeight="1">
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="L15" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-    </row>
-    <row r="15" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="L15" s="6" t="s">
+    <row r="16" spans="2:15" ht="20" customHeight="1">
+      <c r="L16" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="L16" t="s">
+    <row r="17" spans="6:14" ht="20" customHeight="1">
+      <c r="F17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L17" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="L17" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="L18" t="s">
+    <row r="18" spans="6:14" ht="20" customHeight="1"/>
+    <row r="19" spans="6:14" ht="20" customHeight="1">
+      <c r="L19" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F19" s="1" t="s">
+    <row r="20" spans="6:14" ht="20" customHeight="1">
+      <c r="L20" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="M20" s="7" cm="1">
+        <f t="array" ref="M20">SUMPRODUCT((Key!B3:J12&lt;&gt;"#")*(UPPER(B6:J15&amp;"")=UPPER(Key!B3:J12&amp;"")))</f>
+        <v>0</v>
+      </c>
+      <c r="N20" s="5"/>
+    </row>
+    <row r="21" spans="6:14" ht="20" customHeight="1">
+      <c r="L21" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="L19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L21" s="6" t="s">
+      <c r="M21" s="7" cm="1">
+        <f t="array" ref="M21">SUMPRODUCT((Key!B3:J12&lt;&gt;"#")*1)</f>
+        <v>41</v>
+      </c>
+      <c r="N21" s="5"/>
+    </row>
+    <row r="22" spans="6:14" ht="20" customHeight="1">
+      <c r="L22" s="5" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="22" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="L22" t="s">
-        <v>37</v>
-      </c>
-      <c r="M22" s="5" cm="1">
-        <f t="array" ref="M22">SUMPRODUCT((Key!B3:J12&lt;&gt;"#")*(UPPER(B8:J17&amp;"")=UPPER(Key!B3:J12&amp;"")))</f>
+      <c r="M22" s="8">
+        <f>M20/M21</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="L23" t="s">
-        <v>38</v>
-      </c>
-      <c r="M23" s="5" cm="1">
-        <f t="array" ref="M23">SUMPRODUCT((Key!B3:J12&lt;&gt;"#")*1)</f>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="L24" t="s">
-        <v>39</v>
-      </c>
-      <c r="M24" s="7">
-        <f>M22/M23</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="N22" s="5"/>
+    </row>
+    <row r="23" spans="6:14" ht="20" customHeight="1"/>
   </sheetData>
-  <conditionalFormatting sqref="B8:J17">
+  <mergeCells count="2">
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="B3:O3"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B6:J15">
     <cfRule type="expression" dxfId="0" priority="3">
-      <formula>B8&lt;&gt;""</formula>
+      <formula>B6&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -904,7 +985,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="expression" priority="2" stopIfTrue="1" id="{4E0BECEB-A57B-D249-BC5C-464FB2372810}">
-            <xm:f>UPPER(B8)=UPPER(Key!B3)</xm:f>
+            <xm:f>UPPER(B6)=UPPER(Key!B3)</xm:f>
             <x14:dxf>
               <font>
                 <color rgb="FF008121"/>
@@ -916,7 +997,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>B8:J17</xm:sqref>
+          <xm:sqref>B6:J15</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -927,308 +1008,308 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37BC4D0B-A798-5B4B-8526-6305D5F685C2}">
   <dimension ref="B1:J13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="11" width="3.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:10" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="8" t="s">
+    <row r="1" spans="2:10" ht="20" customHeight="1"/>
+    <row r="2" spans="2:10" ht="20" customHeight="1">
+      <c r="B2" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" ht="20" customHeight="1">
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" ht="20" customHeight="1">
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="2:10" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
+      <c r="D4" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" ht="20" customHeight="1">
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" t="s">
+        <v>3</v>
+      </c>
+      <c r="J5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" ht="20" customHeight="1">
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" ht="20" customHeight="1">
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" t="s">
+        <v>3</v>
+      </c>
+      <c r="G7" t="s">
+        <v>3</v>
+      </c>
+      <c r="H7" t="s">
+        <v>3</v>
+      </c>
+      <c r="I7" t="s">
+        <v>3</v>
+      </c>
+      <c r="J7" t="s">
         <v>6</v>
       </c>
-      <c r="D3" t="s">
+    </row>
+    <row r="8" spans="2:10" ht="20" customHeight="1">
+      <c r="B8" t="s">
         <v>6</v>
       </c>
-      <c r="E3" t="s">
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" ht="20" customHeight="1">
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" ht="20" customHeight="1">
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" ht="20" customHeight="1">
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>3</v>
+      </c>
+      <c r="G11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H11" t="s">
+        <v>3</v>
+      </c>
+      <c r="I11" t="s">
+        <v>3</v>
+      </c>
+      <c r="J11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" ht="20" customHeight="1">
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
         <v>6</v>
       </c>
-      <c r="G3" t="s">
+      <c r="F12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" t="s">
         <v>7</v>
       </c>
-      <c r="H3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="2:10" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="H12" t="s">
         <v>9</v>
       </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" t="s">
-        <v>6</v>
-      </c>
-      <c r="I5" t="s">
-        <v>6</v>
-      </c>
-      <c r="J5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I7" t="s">
-        <v>6</v>
-      </c>
-      <c r="J7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" t="s">
-        <v>6</v>
-      </c>
-      <c r="J8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" t="s">
-        <v>6</v>
-      </c>
-      <c r="G9" t="s">
-        <v>6</v>
-      </c>
-      <c r="H9" t="s">
-        <v>6</v>
-      </c>
-      <c r="I9" t="s">
-        <v>6</v>
-      </c>
-      <c r="J9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" t="s">
-        <v>6</v>
-      </c>
-      <c r="I10" t="s">
-        <v>6</v>
-      </c>
-      <c r="J10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>6</v>
-      </c>
-      <c r="G11" t="s">
-        <v>6</v>
-      </c>
-      <c r="H11" t="s">
-        <v>6</v>
-      </c>
-      <c r="I11" t="s">
-        <v>6</v>
-      </c>
-      <c r="J11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" t="s">
-        <v>10</v>
-      </c>
-      <c r="H12" t="s">
-        <v>12</v>
-      </c>
       <c r="I12" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" ht="20" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
